--- a/templates/キャリアウィンクES.xlsx
+++ b/templates/キャリアウィンクES.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EX_174E\Desktop\商談企業\★り_リクルートスタッフィング\エントリーシート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daikisaito/Library/Containers/com.apple.mail/Data/Library/Mail Downloads/B04C7503-6797-49D5-88AA-4218BBA28017/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19CB60F9-3383-47B8-985E-7C030877F886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1840AA0-7615-344D-9C49-9C110F811F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0CA66181-2A21-4410-8C30-7D9B70B8E2DF}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{0CA66181-2A21-4410-8C30-7D9B70B8E2DF}"/>
   </bookViews>
   <sheets>
     <sheet name="エントリーシート" sheetId="5" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <sheet name="Sheet1" sheetId="3" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'(記入例)エントリーシート'!$B$1:$F$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">エントリーシート!$B$1:$F$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'(記入例)エントリーシート'!$B$1:$F$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">エントリーシート!$B$1:$F$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="117">
   <si>
     <t>電話番号</t>
   </si>
@@ -91,30 +91,9 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>愛知県</t>
-    <rPh sb="0" eb="3">
-      <t>アイチケン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>関西</t>
     <rPh sb="0" eb="2">
       <t>カンサイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>宮城</t>
-    <rPh sb="0" eb="2">
-      <t>ミヤギ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>福岡</t>
-    <rPh sb="0" eb="2">
-      <t>フクオカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -998,6 +977,398 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>引っ越し予定の有無</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ウム</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>有り</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>無し</t>
+    <rPh sb="0" eb="1">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">引っ越しの時期と場所
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>※引っ越し予定が有の場合のみ</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇月頃に〇〇県〇〇市付近へ引っ越し</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>担当者名</t>
+    <rPh sb="0" eb="4">
+      <t>タントウシャメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>紹介会社様情報</t>
+    <rPh sb="0" eb="2">
+      <t>ショウカイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガイシャ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>サマ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>企業名</t>
+    <rPh sb="0" eb="3">
+      <t>キギョウメイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>株式会社エクスオード</t>
+    <rPh sb="0" eb="3">
+      <t>カブシキガイシャ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山田 太郎</t>
+    <rPh sb="2" eb="4">
+      <t>タロウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>・面接希望時間帯</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>※10:00~19:45終了まで</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>開始時刻と終了時刻をご記載ください</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">）
+・面接空き枠は、以下URLよりご確認ください。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://docs.google.com/spreadsheets/d/1wiOLlorZl5FfeOm7ncy-8OP9O-TcenlwuydtXRGrldg/edit?usp=sharing</t>
+    </r>
+    <rPh sb="1" eb="3">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>キボウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カイシ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ジコク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ジコク</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>メンセツ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="50" eb="51">
+      <t>ワク</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="61" eb="63">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4月上旬</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4月中旬</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チュウジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4月下旬</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5月上旬</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5月中旬</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チュウジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5月下旬</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6月上旬</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6月中旬</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チュウジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6月下旬</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゲジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7月上旬</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジョウジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>7月中旬</t>
+    <rPh sb="1" eb="2">
+      <t>ガツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>チュウジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>東京都</t>
+    <rPh sb="0" eb="2">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>神奈川県</t>
+    <rPh sb="0" eb="3">
+      <t>カナガワ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>千葉県</t>
+    <rPh sb="0" eb="2">
+      <t>チバ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>埼玉県</t>
+    <rPh sb="0" eb="2">
+      <t>サイタマ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>愛知県</t>
+    <rPh sb="0" eb="2">
+      <t>アイチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>宮城県</t>
+    <rPh sb="0" eb="2">
+      <t>ミヤギ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -1007,7 +1378,7 @@
     <numFmt numFmtId="176" formatCode="0&quot;歳&quot;"/>
     <numFmt numFmtId="177" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;\(aaa\)"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1145,6 +1516,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1172,7 +1551,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -1416,6 +1795,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1425,7 +1815,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1452,12 +1842,6 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1498,14 +1882,6 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="22" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1572,8 +1948,44 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="10" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1599,6 +2011,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1608,13 +2029,30 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1637,23 +2075,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="32">
     <dxf>
       <font>
         <color theme="0" tint="-0.499984740745262"/>
@@ -1703,6 +2131,20 @@
         <color theme="0" tint="-0.499984740745262"/>
       </font>
       <numFmt numFmtId="182" formatCode=";;;&quot;2024年7月31(水)&quot;"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1783,6 +2225,12 @@
         <color theme="0" tint="-0.499984740745262"/>
       </font>
       <numFmt numFmtId="182" formatCode=";;;&quot;2024年7月31(水)&quot;"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+      <numFmt numFmtId="183" formatCode=";;;&quot;09012345678&quot;"/>
     </dxf>
     <dxf>
       <font>
@@ -2149,372 +2597,451 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D3CFCC7-00F3-4385-98E8-513EDC9FA76E}">
-  <dimension ref="B1:I23"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="B1:I27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1"/>
-    <col min="3" max="3" width="31.58203125" customWidth="1"/>
-    <col min="4" max="4" width="20.58203125" customWidth="1"/>
-    <col min="5" max="5" width="34.08203125" customWidth="1"/>
-    <col min="6" max="6" width="20.58203125" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="31.6640625" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="2:9">
       <c r="B1" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="11"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="2:9" ht="19" thickBot="1">
+      <c r="B2" s="9"/>
       <c r="C2" s="2"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B3" s="51" t="s">
-        <v>13</v>
+    <row r="3" spans="2:9" ht="20" thickBot="1">
+      <c r="B3" s="50" t="s">
+        <v>95</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="12"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+        <v>96</v>
+      </c>
+      <c r="D3" s="10"/>
       <c r="G3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B4" s="52"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="20" thickBot="1">
+      <c r="B4" s="50"/>
       <c r="C4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="15"/>
+        <v>94</v>
+      </c>
+      <c r="D4" s="10"/>
       <c r="G4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B5" s="52"/>
+    <row r="5" spans="2:9" ht="20" thickBot="1">
+      <c r="B5" s="61" t="s">
+        <v>10</v>
+      </c>
       <c r="C5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="20" thickBot="1">
+      <c r="B6" s="62"/>
+      <c r="C6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="13"/>
+      <c r="G6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="20" thickBot="1">
+      <c r="B7" s="62"/>
+      <c r="C7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="16"/>
-      <c r="G5" t="s">
+      <c r="D7" s="12"/>
+      <c r="E7" s="14"/>
+      <c r="G7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B6" s="52"/>
-      <c r="C6" s="5" t="s">
+    <row r="8" spans="2:9" ht="20" thickBot="1">
+      <c r="B8" s="62"/>
+      <c r="C8" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="16"/>
-      <c r="G6" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="6" t="str">
-        <f>D6&amp;"/"&amp;E6&amp;"/"&amp;F6</f>
-        <v>//</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="52"/>
-      <c r="C7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="8" t="str">
-        <f ca="1">IF(D6="","",DATEDIF($I$6,TODAY(),"Y"))</f>
-        <v/>
-      </c>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B8" s="52"/>
-      <c r="C8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="18"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="14"/>
       <c r="G8" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="2:9" ht="30" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B9" s="52"/>
-      <c r="C9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="46"/>
+      <c r="I8" s="6" t="str">
+        <f>D8&amp;"/"&amp;E8&amp;"/"&amp;F8</f>
+        <v>//</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="20" thickBot="1">
+      <c r="B9" s="62"/>
+      <c r="C9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="8" t="str">
+        <f ca="1">IF(D8="","",DATEDIF($I$8,TODAY(),"Y"))</f>
+        <v/>
+      </c>
       <c r="G9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B10" s="52"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="20" thickBot="1">
+      <c r="B10" s="62"/>
       <c r="C10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="42"/>
+        <v>39</v>
+      </c>
+      <c r="D10" s="16"/>
       <c r="G10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="30" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B11" s="52"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="33" thickBot="1">
+      <c r="B11" s="62"/>
       <c r="C11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="47"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="49"/>
+        <v>11</v>
+      </c>
+      <c r="D11" s="51"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="53"/>
       <c r="G11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B12" s="52"/>
+    <row r="12" spans="2:9" ht="20" thickBot="1">
+      <c r="B12" s="62"/>
       <c r="C12" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12"/>
-      <c r="F12" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="D12" s="37"/>
+      <c r="E12" s="38"/>
       <c r="G12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B13" s="53"/>
+    <row r="13" spans="2:9" ht="33" thickBot="1">
+      <c r="B13" s="62"/>
       <c r="C13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="18"/>
+        <v>12</v>
+      </c>
+      <c r="D13" s="54"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="56"/>
       <c r="G13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B14" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>62</v>
-      </c>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="20" thickBot="1">
+      <c r="B14" s="62"/>
+      <c r="C14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="F14" s="4"/>
       <c r="G14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B15" s="44"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="21"/>
-    </row>
-    <row r="16" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B16" s="44"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="22"/>
-    </row>
-    <row r="17" spans="2:7" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B17" s="44"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="22"/>
-    </row>
-    <row r="18" spans="2:7" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B18" s="44"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="22"/>
-    </row>
-    <row r="19" spans="2:7" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B19" s="44"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="22"/>
-    </row>
-    <row r="20" spans="2:7" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B20" s="44"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="22"/>
-    </row>
-    <row r="21" spans="2:7" ht="31" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B21" s="44"/>
-      <c r="C21" s="66" t="s">
-        <v>91</v>
-      </c>
-      <c r="D21" s="64"/>
-      <c r="G21" t="s">
+    <row r="15" spans="2:9" ht="20" thickBot="1">
+      <c r="B15" s="62"/>
+      <c r="C15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="G15" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="29" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B22" s="44"/>
-      <c r="C22" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="23"/>
-      <c r="G22" t="s">
+    <row r="16" spans="2:9" ht="20" thickBot="1">
+      <c r="B16" s="62"/>
+      <c r="C16" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="44"/>
+      <c r="G16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B23" s="44"/>
-      <c r="C23" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="50"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="49"/>
-      <c r="G23" t="s">
+    <row r="17" spans="2:7" ht="33" thickBot="1">
+      <c r="B17" s="63"/>
+      <c r="C17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="64"/>
+      <c r="E17" s="65"/>
+      <c r="F17" s="66"/>
+      <c r="G17" t="s">
         <v>1</v>
       </c>
     </row>
+    <row r="18" spans="2:7" ht="84" customHeight="1" thickBot="1">
+      <c r="B18" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="69" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" s="70"/>
+    </row>
+    <row r="19" spans="2:7" ht="19" thickBot="1">
+      <c r="B19" s="50"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="68"/>
+      <c r="G19" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="19" thickBot="1">
+      <c r="B20" s="50"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="68"/>
+    </row>
+    <row r="21" spans="2:7" ht="19" thickBot="1">
+      <c r="B21" s="50"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="68"/>
+    </row>
+    <row r="22" spans="2:7" ht="19" thickBot="1">
+      <c r="B22" s="50"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="68"/>
+    </row>
+    <row r="23" spans="2:7" ht="19" thickBot="1">
+      <c r="B23" s="50"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="68"/>
+    </row>
+    <row r="24" spans="2:7" ht="19" thickBot="1">
+      <c r="B24" s="50"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="68"/>
+    </row>
+    <row r="25" spans="2:7" ht="31" customHeight="1" thickBot="1">
+      <c r="B25" s="50"/>
+      <c r="C25" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="40"/>
+      <c r="G25" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="31" thickBot="1">
+      <c r="B26" s="50"/>
+      <c r="C26" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="19"/>
+      <c r="G26" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="46.5" customHeight="1" thickBot="1">
+      <c r="B27" s="50"/>
+      <c r="C27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="57"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="56"/>
+      <c r="G27" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B14:B23"/>
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="15">
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B18:B27"/>
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="B3:B13"/>
-    <mergeCell ref="C14:C20"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="C18:C24"/>
+    <mergeCell ref="B5:B17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E18:F18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="D3 D4:E5 D6:F6 D8 D9:F9 D10:E10 D11:F11 D12:D13 E15:E20 D15:D22">
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+  <conditionalFormatting sqref="D3:D5 D6:E7 D8:F8 D10 D11:F11 D12:E12 D13:F13 D14:D17 E19:E24 D19:D26">
+    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
       <formula>""""""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:D6 E4:E6 F6 D8 D9:F9 D10:E10 D11:F11 D12:D13 D15:E20 D21:D22">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+  <conditionalFormatting sqref="D3:D8 E6:E8 F8 D10 D11:F11 D12:E12 D13:F13 D14:D17 D19:E19 E20:E24 D20:D26">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="cellIs" dxfId="26" priority="12" operator="equal">
+  <conditionalFormatting sqref="D6">
+    <cfRule type="cellIs" dxfId="29" priority="13" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5">
-    <cfRule type="cellIs" dxfId="25" priority="11" operator="equal">
-      <formula>" "</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9">
-    <cfRule type="cellIs" dxfId="24" priority="9" operator="equal">
-      <formula>" "</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D10">
-    <cfRule type="cellIs" dxfId="23" priority="8" operator="equal">
+  <conditionalFormatting sqref="D7">
+    <cfRule type="cellIs" dxfId="28" priority="12" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11">
-    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="10" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="cellIs" dxfId="21" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="9" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D15">
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
+  <conditionalFormatting sqref="D13">
+    <cfRule type="cellIs" dxfId="25" priority="7" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="cellIs" dxfId="19" priority="13" operator="equal">
+  <conditionalFormatting sqref="D14">
+    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="cellIs" dxfId="18" priority="10" operator="equal">
+  <conditionalFormatting sqref="D17">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
+  <conditionalFormatting sqref="D19">
+    <cfRule type="cellIs" dxfId="22" priority="5" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E15">
-    <cfRule type="cellIs" dxfId="16" priority="3" operator="equal">
+  <conditionalFormatting sqref="E6">
+    <cfRule type="cellIs" dxfId="21" priority="14" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E7">
+    <cfRule type="cellIs" dxfId="20" priority="11" operator="equal">
+      <formula>" "</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E12">
+    <cfRule type="cellIs" dxfId="19" priority="8" operator="equal">
+      <formula>" "</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19:E24">
+    <cfRule type="cellIs" dxfId="18" priority="4" operator="equal">
+      <formula>" "</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D12" xr:uid="{AB15105F-A633-47B2-8897-EF6F7BA117F3}">
+      <formula1>3</formula1>
+    </dataValidation>
+    <dataValidation type="textLength" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12" xr:uid="{92C21E0E-37C2-4AD3-BABA-31027BBF96F3}">
+      <formula1>4</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BDB538A9-AE22-43D0-A33C-90175BF7C9B7}">
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$13</xm:f>
           </x14:formula1>
-          <xm:sqref>E6</xm:sqref>
+          <xm:sqref>E8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B9EBEE33-DB0F-419C-B43B-3F33549F8B84}">
           <x14:formula1>
             <xm:f>Sheet1!$C$2:$C$32</xm:f>
           </x14:formula1>
-          <xm:sqref>F6</xm:sqref>
+          <xm:sqref>F8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C57CF34A-E50D-4D67-BB59-675ADFE9A108}">
           <x14:formula1>
             <xm:f>Sheet1!$G$2:$G$3</xm:f>
           </x14:formula1>
-          <xm:sqref>D22</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E9753D79-57AE-416C-A7F4-8F397A503DE1}">
-          <x14:formula1>
-            <xm:f>Sheet1!$D$2:$D$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>D3</xm:sqref>
+          <xm:sqref>D26</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F52526C4-381F-4BC5-972F-55ECCF78F201}">
           <x14:formula1>
             <xm:f>Sheet1!$H$2:$H$3</xm:f>
           </x14:formula1>
-          <xm:sqref>D8</xm:sqref>
+          <xm:sqref>D10</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D991DE7F-AA7B-4BCD-A995-CDE2BD8D18CC}">
           <x14:formula1>
             <xm:f>Sheet1!$F$2:$F$7</xm:f>
           </x14:formula1>
-          <xm:sqref>D13</xm:sqref>
+          <xm:sqref>D15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D9600205-DF9C-48E5-864A-9154B5B8DB5C}">
           <x14:formula1>
-            <xm:f>Sheet1!$A$2:$A$20</xm:f>
+            <xm:f>Sheet1!$A$2:$A$21</xm:f>
           </x14:formula1>
-          <xm:sqref>D6</xm:sqref>
+          <xm:sqref>D8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E7B36755-B29B-4DDB-B49A-77F603D8378C}">
           <x14:formula1>
-            <xm:f>Sheet2!$C$2:$C$26</xm:f>
+            <xm:f>Sheet2!$C$2:$C$37</xm:f>
           </x14:formula1>
-          <xm:sqref>D21</xm:sqref>
+          <xm:sqref>D25</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{17C95061-2F57-4F1B-8125-54ACF95564DC}">
+          <x14:formula1>
+            <xm:f>Sheet1!$I$2:$I$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D16</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E9753D79-57AE-416C-A7F4-8F397A503DE1}">
+          <x14:formula1>
+            <xm:f>Sheet1!$D$2:$D$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>D5</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2524,457 +3051,520 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BB4AB1E-EF3B-4107-BD09-8F3C40FE8F99}">
-  <dimension ref="B1:I23"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="B1:I27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
     <col min="3" max="3" width="31.5" customWidth="1"/>
-    <col min="4" max="4" width="20.58203125" customWidth="1"/>
-    <col min="5" max="5" width="33.25" customWidth="1"/>
-    <col min="6" max="6" width="20.58203125" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="33.1640625" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="2:9">
       <c r="B1" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B2" s="11"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="2:9" ht="19" thickBot="1">
+      <c r="B2" s="9"/>
       <c r="C2" s="2"/>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B3" s="51" t="s">
-        <v>13</v>
+    <row r="3" spans="2:9" ht="20" thickBot="1">
+      <c r="B3" s="50" t="s">
+        <v>95</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
+        <v>96</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>97</v>
+      </c>
       <c r="G3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B4" s="52"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="20" thickBot="1">
+      <c r="B4" s="50"/>
       <c r="C4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="F4" s="28"/>
+        <v>94</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>98</v>
+      </c>
       <c r="G4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B5" s="52"/>
+    <row r="5" spans="2:9" ht="20" thickBot="1">
+      <c r="B5" s="61" t="s">
+        <v>10</v>
+      </c>
       <c r="C5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" ht="20" thickBot="1">
+      <c r="B6" s="62"/>
+      <c r="C6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="24"/>
+      <c r="G6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="20" thickBot="1">
+      <c r="B7" s="62"/>
+      <c r="C7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D7" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="28"/>
-      <c r="G5" t="s">
+      <c r="F7" s="24"/>
+      <c r="G7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B6" s="52"/>
-      <c r="C6" s="5" t="s">
+    <row r="8" spans="2:9" ht="20" thickBot="1">
+      <c r="B8" s="62"/>
+      <c r="C8" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D8" s="25">
         <v>1998</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E8" s="27">
         <v>1</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F8" s="26">
         <v>1</v>
       </c>
-      <c r="G6" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="6" t="str">
-        <f>D6&amp;"/"&amp;E6&amp;"/"&amp;F6</f>
-        <v>1998/1/1</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B7" s="52"/>
-      <c r="C7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="8">
-        <f ca="1">IF(D6="","",DATEDIF($I$6,TODAY(),"Y"))</f>
-        <v>27</v>
-      </c>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B8" s="52"/>
-      <c r="C8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
       <c r="G8" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="2:9" ht="30" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B9" s="52"/>
-      <c r="C9" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="57" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="59"/>
+      <c r="I8" s="6" t="str">
+        <f>D8&amp;"/"&amp;E8&amp;"/"&amp;F8</f>
+        <v>1998/1/1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="20" thickBot="1">
+      <c r="B9" s="62"/>
+      <c r="C9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="8">
+        <f ca="1">IF(D8="","",DATEDIF($I$8,TODAY(),"Y"))</f>
+        <v>28</v>
+      </c>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
       <c r="G9" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B10" s="52"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" ht="20" thickBot="1">
+      <c r="B10" s="62"/>
       <c r="C10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="33">
-        <v>1234</v>
-      </c>
-      <c r="F10" s="28"/>
+        <v>39</v>
+      </c>
+      <c r="D10" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
       <c r="G10" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" ht="30" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B11" s="52"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9" ht="33" thickBot="1">
+      <c r="B11" s="62"/>
       <c r="C11" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="60" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="58"/>
-      <c r="F11" s="59"/>
+        <v>11</v>
+      </c>
+      <c r="D11" s="71" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="72"/>
+      <c r="F11" s="73"/>
       <c r="G11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B12" s="52"/>
+    <row r="12" spans="2:9" ht="20" thickBot="1">
+      <c r="B12" s="62"/>
       <c r="C12" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="35"/>
+        <v>28</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="29">
+        <v>1234</v>
+      </c>
+      <c r="F12" s="24"/>
       <c r="G12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B13" s="53"/>
+    <row r="13" spans="2:9" ht="33" thickBot="1">
+      <c r="B13" s="62"/>
       <c r="C13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
+        <v>12</v>
+      </c>
+      <c r="D13" s="74" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="72"/>
+      <c r="F13" s="73"/>
       <c r="G13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="2:9" ht="56.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B14" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="54" t="s">
-        <v>58</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>62</v>
-      </c>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" ht="20" thickBot="1">
+      <c r="B14" s="62"/>
+      <c r="C14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="24"/>
+      <c r="F14" s="31"/>
       <c r="G14" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B15" s="44"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="36">
+    <row r="15" spans="2:9" ht="20" thickBot="1">
+      <c r="B15" s="62"/>
+      <c r="C15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="20" thickBot="1">
+      <c r="B16" s="62"/>
+      <c r="C16" s="43" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+    </row>
+    <row r="17" spans="2:7" ht="33" thickBot="1">
+      <c r="B17" s="63"/>
+      <c r="C17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="48"/>
+      <c r="F17" s="49"/>
+    </row>
+    <row r="18" spans="2:7" ht="56.25" customHeight="1" thickBot="1">
+      <c r="B18" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="58" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="19" thickBot="1">
+      <c r="B19" s="50"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="32">
         <v>45701</v>
       </c>
-      <c r="E15" s="37" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B16" s="44"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="36">
+      <c r="E19" s="33" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="19" thickBot="1">
+      <c r="B20" s="50"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="32">
         <v>45702</v>
       </c>
-      <c r="E16" s="39" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B17" s="44"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="38">
+      <c r="E20" s="35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="19" thickBot="1">
+      <c r="B21" s="50"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="34">
         <v>45704</v>
       </c>
-      <c r="E17" s="39" t="s">
+      <c r="E21" s="35" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="19" thickBot="1">
+      <c r="B22" s="50"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="34">
+        <v>45707</v>
+      </c>
+      <c r="E22" s="35" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="19" thickBot="1">
+      <c r="B23" s="50"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="34">
+        <v>45708</v>
+      </c>
+      <c r="E23" s="35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="19" thickBot="1">
+      <c r="B24" s="50"/>
+      <c r="C24" s="60"/>
+      <c r="D24" s="34">
+        <v>45709</v>
+      </c>
+      <c r="E24" s="33" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B18" s="44"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="38">
-        <v>45707</v>
-      </c>
-      <c r="E18" s="39" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B19" s="44"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="38">
-        <v>45708</v>
-      </c>
-      <c r="E19" s="39" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="18.5" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B20" s="44"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="38">
-        <v>45709</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B21" s="44"/>
-      <c r="C21" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="65" t="s">
-        <v>67</v>
-      </c>
-      <c r="G21" t="s">
+    <row r="25" spans="2:7" ht="33" customHeight="1" thickBot="1">
+      <c r="B25" s="50"/>
+      <c r="C25" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="D25" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="29" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B22" s="44"/>
-      <c r="C22" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" t="s">
+    <row r="26" spans="2:7" ht="31" thickBot="1">
+      <c r="B26" s="50"/>
+      <c r="C26" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="2:7" ht="46.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B23" s="44"/>
-      <c r="C23" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="62"/>
-      <c r="F23" s="63"/>
-      <c r="G23" t="s">
+    <row r="27" spans="2:7" ht="46.5" customHeight="1" thickBot="1">
+      <c r="B27" s="50"/>
+      <c r="C27" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="75" t="s">
+        <v>53</v>
+      </c>
+      <c r="E27" s="76"/>
+      <c r="F27" s="77"/>
+      <c r="G27" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B3:B13"/>
-    <mergeCell ref="D9:F9"/>
+  <mergeCells count="7">
+    <mergeCell ref="B3:B4"/>
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="B14:B23"/>
-    <mergeCell ref="C14:C20"/>
-    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="B18:B27"/>
+    <mergeCell ref="C18:C24"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B5:B17"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <conditionalFormatting sqref="D3 D4:E5 D8 D9:F9 E10 D11 D13 E15:E20 D15:D22 D17:E19">
-    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
+  <conditionalFormatting sqref="D5 D6:E7 D10 D11:F11 E12 D13 E19:E24 D19:D26 D21:E23">
+    <cfRule type="cellIs" dxfId="17" priority="11" operator="equal">
       <formula>""""""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:D6">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+  <conditionalFormatting sqref="D5:D8">
+    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4">
-    <cfRule type="cellIs" dxfId="13" priority="17" operator="equal">
+  <conditionalFormatting sqref="D6">
+    <cfRule type="cellIs" dxfId="15" priority="21" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5">
-    <cfRule type="cellIs" dxfId="12" priority="16" operator="equal">
-      <formula>" "</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9">
-    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
-      <formula>" "</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D10">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+  <conditionalFormatting sqref="D7">
+    <cfRule type="cellIs" dxfId="14" priority="20" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11">
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="18" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D12">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D15:D16">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+  <conditionalFormatting sqref="D13">
+    <cfRule type="cellIs" dxfId="11" priority="15" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6:F6">
-    <cfRule type="cellIs" dxfId="6" priority="5" operator="equal">
+  <conditionalFormatting sqref="D14">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
+      <formula>" "</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15:D17">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+      <formula>""</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>""""""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4">
-    <cfRule type="cellIs" dxfId="5" priority="18" operator="equal">
+  <conditionalFormatting sqref="D19:D20">
+    <cfRule type="cellIs" dxfId="7" priority="13" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E4:E6 F6 D8 D9:F9 E10 D11 D13 D15:E20 D21:D22">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+  <conditionalFormatting sqref="D8:F8">
+    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+      <formula>""""""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6">
+    <cfRule type="cellIs" dxfId="5" priority="22" operator="equal">
+      <formula>" "</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6:E8 F8 D10 D11:F11 E12 D13 D19:E24 D25:D26">
+    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
       <formula>""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5">
-    <cfRule type="cellIs" dxfId="3" priority="15" operator="equal">
+  <conditionalFormatting sqref="E7">
+    <cfRule type="cellIs" dxfId="3" priority="19" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="cellIs" dxfId="2" priority="12" operator="equal">
+  <conditionalFormatting sqref="E12">
+    <cfRule type="cellIs" dxfId="2" priority="16" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E15">
-    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
+  <conditionalFormatting sqref="E19">
+    <cfRule type="cellIs" dxfId="1" priority="12" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E20">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="E24">
+    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="D9" r:id="rId1" xr:uid="{EB5318A3-D619-4369-B912-79B53B29D68D}"/>
+    <hyperlink ref="D11" r:id="rId1" xr:uid="{EB5318A3-D619-4369-B912-79B53B29D68D}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="84" orientation="portrait" r:id="rId2"/>
   <ignoredErrors>
-    <ignoredError sqref="D12 D10" numberStoredAsText="1"/>
+    <ignoredError sqref="D14 D12" numberStoredAsText="1"/>
   </ignoredErrors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C79921A6-6655-49B6-81D3-919FFA0F188C}">
           <x14:formula1>
             <xm:f>Sheet1!$H$2:$H$3</xm:f>
           </x14:formula1>
-          <xm:sqref>D8</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4D6EB9A5-A701-4478-9E8C-9B81AD2E41A1}">
-          <x14:formula1>
-            <xm:f>Sheet1!$D$2:$D$6</xm:f>
-          </x14:formula1>
-          <xm:sqref>D3</xm:sqref>
+          <xm:sqref>D10</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6B5212ED-07B1-4D0C-BC53-D5C0B8553F5A}">
           <x14:formula1>
             <xm:f>Sheet1!$G$2:$G$3</xm:f>
           </x14:formula1>
-          <xm:sqref>D22</xm:sqref>
+          <xm:sqref>D26</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{98AE176A-ADA8-40E6-90D1-144FF195402D}">
           <x14:formula1>
             <xm:f>Sheet1!$C$2:$C$32</xm:f>
           </x14:formula1>
-          <xm:sqref>F6</xm:sqref>
+          <xm:sqref>F8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AE9A494A-0D48-42EB-9C33-2BE6F83E05D5}">
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$13</xm:f>
           </x14:formula1>
-          <xm:sqref>E6</xm:sqref>
+          <xm:sqref>E8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BE34B861-B875-43FC-A857-61C0B03D6145}">
           <x14:formula1>
             <xm:f>Sheet1!$F$2:$F$7</xm:f>
           </x14:formula1>
-          <xm:sqref>D13</xm:sqref>
+          <xm:sqref>D15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{36C039F5-E07E-4A45-927E-F908C0F3517D}">
           <x14:formula1>
             <xm:f>Sheet1!$A$2:$A$20</xm:f>
           </x14:formula1>
-          <xm:sqref>D6</xm:sqref>
+          <xm:sqref>D8</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BBC856D2-5608-4AE5-B02A-CCEABC2058A6}">
+          <x14:formula1>
+            <xm:f>Sheet1!$I$2:$I$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>D16</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4D6EB9A5-A701-4478-9E8C-9B81AD2E41A1}">
+          <x14:formula1>
+            <xm:f>Sheet1!$D$2:$D$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>D5</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2984,135 +3574,190 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{309F1AD1-7840-44D8-9869-22217F06E45B}">
-  <dimension ref="B2:C26"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="B2:C37"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:3">
       <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3">
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3">
+      <c r="C4" t="s">
         <v>65</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="5" spans="2:3">
+      <c r="C5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C3" t="s">
+    <row r="6" spans="2:3">
+      <c r="C6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" t="s">
+    <row r="7" spans="2:3">
+      <c r="C7" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" t="s">
+    <row r="8" spans="2:3">
+      <c r="C8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C6" t="s">
+    <row r="9" spans="2:3">
+      <c r="C9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C7" t="s">
+    <row r="10" spans="2:3">
+      <c r="C10" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C8" t="s">
+    <row r="11" spans="2:3">
+      <c r="C11" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C9" t="s">
+    <row r="12" spans="2:3">
+      <c r="C12" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C10" t="s">
+    <row r="13" spans="2:3">
+      <c r="C13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" t="s">
+    <row r="14" spans="2:3">
+      <c r="C14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C12" t="s">
+    <row r="15" spans="2:3">
+      <c r="C15" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C13" t="s">
+    <row r="16" spans="2:3">
+      <c r="C16" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C14" t="s">
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C15" t="s">
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C16" t="s">
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C17" t="s">
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C18" t="s">
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C19" t="s">
+    <row r="22" spans="3:3">
+      <c r="C22" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C20" t="s">
+    <row r="23" spans="3:3">
+      <c r="C23" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C21" t="s">
+    <row r="24" spans="3:3">
+      <c r="C24" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C22" t="s">
+    <row r="25" spans="3:3">
+      <c r="C25" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C23" t="s">
+    <row r="26" spans="3:3">
+      <c r="C26" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="3:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C24" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25" spans="3:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C25" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="C26" t="s">
-        <v>90</v>
+    <row r="27" spans="3:3">
+      <c r="C27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" spans="3:3">
+      <c r="C31" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3">
+      <c r="C32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="33" spans="3:3">
+      <c r="C33" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="3:3">
+      <c r="C34" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="35" spans="3:3">
+      <c r="C35" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="36" spans="3:3">
+      <c r="C36" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="3:3">
+      <c r="C37" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -3123,10 +3768,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E1CF9EC-CBD7-4B97-BC0E-B05AE34F25DE}">
-  <dimension ref="A2:H32"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A2:I32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:9">
       <c r="A2">
         <v>1989</v>
       </c>
@@ -3137,22 +3782,25 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
         <v>30</v>
       </c>
-      <c r="F2" t="s">
-        <v>33</v>
-      </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>40</v>
+      </c>
+      <c r="I2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3">
         <v>1990</v>
       </c>
@@ -3163,22 +3811,25 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>41</v>
+      </c>
+      <c r="I3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4">
         <v>1991</v>
       </c>
@@ -3189,16 +3840,16 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>9</v>
+        <v>113</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5">
         <v>1992</v>
       </c>
@@ -3209,16 +3860,16 @@
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6">
         <v>1993</v>
       </c>
@@ -3229,16 +3880,16 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7">
         <v>1994</v>
       </c>
@@ -3249,16 +3900,16 @@
         <v>6</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8">
         <v>1995</v>
       </c>
@@ -3268,11 +3919,14 @@
       <c r="C8">
         <v>7</v>
       </c>
+      <c r="D8" t="s">
+        <v>116</v>
+      </c>
       <c r="E8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9">
         <v>1996</v>
       </c>
@@ -3282,11 +3936,14 @@
       <c r="C9">
         <v>8</v>
       </c>
+      <c r="D9" t="s">
+        <v>61</v>
+      </c>
       <c r="E9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10">
         <v>1997</v>
       </c>
@@ -3297,10 +3954,10 @@
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11">
         <v>1998</v>
       </c>
@@ -3311,10 +3968,10 @@
         <v>10</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12">
         <v>1999</v>
       </c>
@@ -3325,10 +3982,10 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13">
         <v>2000</v>
       </c>
@@ -3339,10 +3996,10 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14">
         <v>2001</v>
       </c>
@@ -3350,10 +4007,10 @@
         <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15">
         <v>2002</v>
       </c>
@@ -3361,10 +4018,10 @@
         <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16">
         <v>2003</v>
       </c>
@@ -3372,7 +4029,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>2004</v>
       </c>
@@ -3380,7 +4037,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>2005</v>
       </c>
@@ -3388,7 +4045,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>2006</v>
       </c>
@@ -3396,7 +4053,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>2007</v>
       </c>
@@ -3404,62 +4061,65 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:3">
+      <c r="A21">
+        <v>2008</v>
+      </c>
       <c r="C21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:3">
       <c r="C22">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:3">
       <c r="C23">
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:3">
       <c r="C24">
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:3">
       <c r="C25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:3">
       <c r="C26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:3">
       <c r="C27">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:3">
       <c r="C28">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:3">
       <c r="C29">
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:3">
       <c r="C30">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:3">
       <c r="C31">
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:3">
       <c r="C32">
         <v>31</v>
       </c>
